--- a/TPO/lab3.xlsx
+++ b/TPO/lab3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\labs\labs-6-sem\TPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A16D53-038A-4F25-B4FB-39BAD35F7C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D660A8BF-7389-4BBE-B28E-60A962D4F6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{86E4046E-DEF1-4EF5-B54E-5FBB288D059C}"/>
   </bookViews>
@@ -133,9 +133,6 @@
     <t>тестирование с запуском ПО</t>
   </si>
   <si>
-    <t>любое функциональное тестирование</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -203,6 +200,9 @@
   </si>
   <si>
     <t>Тестирование возможности вставлять изображения в заметку и менять начертание текста</t>
+  </si>
+  <si>
+    <t>удаление администратором любой заметки</t>
   </si>
 </sst>
 </file>
@@ -227,12 +227,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -299,10 +305,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -310,16 +322,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -881,538 +893,571 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:28" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="I4" s="4" t="e" vm="1">
+      <c r="G4" s="5"/>
+      <c r="I4" s="7" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
     </row>
     <row r="5" spans="1:28" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
     </row>
     <row r="6" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
+      <c r="G6" s="5"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
     </row>
     <row r="7" spans="1:28" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
     </row>
     <row r="8" spans="1:28" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
     </row>
     <row r="9" spans="1:28" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+    </row>
+    <row r="10" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-    </row>
-    <row r="10" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="5"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+    </row>
+    <row r="11" spans="1:28" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-    </row>
-    <row r="11" spans="1:28" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="9"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+    </row>
+    <row r="12" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-    </row>
-    <row r="12" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="5"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+    </row>
+    <row r="13" spans="1:28" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-    </row>
-    <row r="13" spans="1:28" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="5"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+    </row>
+    <row r="14" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-    </row>
-    <row r="14" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="5"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+    </row>
+    <row r="15" spans="1:28" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-    </row>
-    <row r="15" spans="1:28" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="5"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+    </row>
+    <row r="16" spans="1:28" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-    </row>
-    <row r="16" spans="1:28" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+    </row>
+    <row r="17" spans="1:28" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="2" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
-    </row>
-    <row r="17" spans="1:28" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I4:AB17"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C15:E15"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:E2"/>
     <mergeCell ref="F1:G2"/>
@@ -1429,39 +1474,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I4:AB17"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
